--- a/csv/policies/reference/Ref_clean electricity/formula_Ref_clean electricity_BC.xlsx
+++ b/csv/policies/reference/Ref_clean electricity/formula_Ref_clean electricity_BC.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Market share_class_min</t>
+          <t>market_share_class_min</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Market share_class_min</t>
+          <t>market_share_class_min</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Market share_class_min</t>
+          <t>market_share_class_min</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Market share_class</t>
+          <t>market_share_class</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Retrofit_existing_min</t>
+          <t>retrofit_existing_min</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
